--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755521587_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.02304251562731821</v>
       </c>
       <c r="C2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>26808324</v>
+        <v>4085093</v>
       </c>
       <c r="L2" t="n">
-        <v>15812697</v>
+        <v>2172967</v>
       </c>
       <c r="M2" t="n">
-        <v>4149013</v>
+        <v>523565</v>
       </c>
       <c r="N2" t="n">
-        <v>249018</v>
+        <v>24402</v>
       </c>
       <c r="O2" t="n">
-        <v>2450537</v>
+        <v>326963</v>
       </c>
       <c r="P2" t="n">
-        <v>988790</v>
+        <v>139650</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999448657035828</v>
+        <v>0.9998725652694702</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9075580835342407</v>
+        <v>0.8297189474105835</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8168820738792419</v>
+        <v>0.6735305190086365</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7403773069381714</v>
+        <v>0.5607404112815857</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5766267776489258</v>
+        <v>0.340967208147049</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8031756281852722</v>
+        <v>0.6431418061256409</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8520085215568542</v>
+        <v>0.7217725515365601</v>
       </c>
       <c r="X2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37276632</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>25940546</v>
+        <v>3984507</v>
       </c>
       <c r="AG2" t="n">
-        <v>14584543</v>
+        <v>2036603</v>
       </c>
       <c r="AH2" t="n">
-        <v>3710241</v>
+        <v>481192</v>
       </c>
       <c r="AI2" t="n">
-        <v>219450</v>
+        <v>22644</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2245041</v>
+        <v>303181</v>
       </c>
       <c r="AK2" t="n">
-        <v>927068</v>
+        <v>131107</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.875588059425354</v>
+        <v>0.8069498538970947</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.7586426734924316</v>
+        <v>0.6356266140937805</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6677120923995972</v>
+        <v>0.5195851922035217</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.4138473272323608</v>
+        <v>0.2562175989151001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.7364836931228638</v>
+        <v>0.5967495441436768</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7994874119758606</v>
+        <v>0.6783864498138428</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.005986791724320211</v>
       </c>
       <c r="C3" t="n">
-        <v>580</v>
+        <v>265</v>
       </c>
       <c r="D3" t="n">
-        <v>26808324</v>
+        <v>4085093</v>
       </c>
       <c r="E3" t="n">
-        <v>2491135</v>
+        <v>747221</v>
       </c>
       <c r="F3" t="n">
-        <v>130106</v>
+        <v>42871</v>
       </c>
       <c r="G3" t="n">
-        <v>23707</v>
+        <v>6546</v>
       </c>
       <c r="H3" t="n">
-        <v>3676</v>
+        <v>1993</v>
       </c>
       <c r="I3" t="n">
-        <v>719</v>
+        <v>262</v>
       </c>
       <c r="J3" t="n">
-        <v>59143713</v>
+        <v>9856836</v>
       </c>
       <c r="K3" t="n">
-        <v>64233515</v>
+        <v>10347776</v>
       </c>
       <c r="L3" t="n">
-        <v>73515790</v>
+        <v>11768709</v>
       </c>
       <c r="M3" t="n">
-        <v>89388327</v>
+        <v>14727328</v>
       </c>
       <c r="N3" t="n">
-        <v>95707640</v>
+        <v>15934398</v>
       </c>
       <c r="O3" t="n">
-        <v>92767401</v>
+        <v>15379237</v>
       </c>
       <c r="P3" t="n">
-        <v>95090625</v>
+        <v>15823128</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.91004478931427</v>
+        <v>0.836380660533905</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8166902661323547</v>
+        <v>0.6689296364784241</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7436614632606506</v>
+        <v>0.5612025856971741</v>
       </c>
       <c r="U3" t="n">
-        <v>0.468144953250885</v>
+        <v>0.2746828496456146</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8022773861885071</v>
+        <v>0.6414284110069275</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8523867726325989</v>
+        <v>0.7219292521476746</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>25940546</v>
+        <v>3984507</v>
       </c>
       <c r="Z3" t="n">
-        <v>3272259</v>
+        <v>830301</v>
       </c>
       <c r="AA3" t="n">
-        <v>162855</v>
+        <v>49557</v>
       </c>
       <c r="AB3" t="n">
-        <v>75253</v>
+        <v>16367</v>
       </c>
       <c r="AC3" t="n">
-        <v>6513</v>
+        <v>3146</v>
       </c>
       <c r="AD3" t="n">
-        <v>821</v>
+        <v>373</v>
       </c>
       <c r="AE3" t="n">
-        <v>59145768</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>63278271</v>
+        <v>10232918</v>
       </c>
       <c r="AG3" t="n">
-        <v>72420495</v>
+        <v>11654492</v>
       </c>
       <c r="AH3" t="n">
-        <v>88996824</v>
+        <v>14692550</v>
       </c>
       <c r="AI3" t="n">
-        <v>95579657</v>
+        <v>15915829</v>
       </c>
       <c r="AJ3" t="n">
-        <v>92564641</v>
+        <v>15355785</v>
       </c>
       <c r="AK3" t="n">
-        <v>95029865</v>
+        <v>15814804</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8805868625640869</v>
+        <v>0.8157867193222046</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.7532588839530945</v>
+        <v>0.6269510984420776</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.665016770362854</v>
+        <v>0.5157835483551025</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.4125581681728363</v>
+        <v>0.2548937797546387</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.7350003719329834</v>
+        <v>0.5947734117507935</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.7991793155670166</v>
+        <v>0.6777657270431519</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.05922733603598913</v>
       </c>
       <c r="C4" t="n">
-        <v>275</v>
+        <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>2583756</v>
+        <v>791384</v>
       </c>
       <c r="E4" t="n">
-        <v>15812697</v>
+        <v>2172967</v>
       </c>
       <c r="F4" t="n">
-        <v>855537</v>
+        <v>241133</v>
       </c>
       <c r="G4" t="n">
-        <v>32078</v>
+        <v>10061</v>
       </c>
       <c r="H4" t="n">
-        <v>70127</v>
+        <v>29188</v>
       </c>
       <c r="I4" t="n">
-        <v>7456</v>
+        <v>3571</v>
       </c>
       <c r="J4" t="n">
-        <v>2055</v>
+        <v>792</v>
       </c>
       <c r="K4" t="n">
-        <v>2730638</v>
+        <v>838373</v>
       </c>
       <c r="L4" t="n">
-        <v>3544684</v>
+        <v>1053267</v>
       </c>
       <c r="M4" t="n">
-        <v>1454904</v>
+        <v>410138</v>
       </c>
       <c r="N4" t="n">
-        <v>182835</v>
+        <v>47165</v>
       </c>
       <c r="O4" t="n">
-        <v>600523</v>
+        <v>181421</v>
       </c>
       <c r="P4" t="n">
-        <v>171750</v>
+        <v>53832</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.999972403049469</v>
+        <v>0.9999362826347351</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9087997078895569</v>
+        <v>0.8330365419387817</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8167861700057983</v>
+        <v>0.6712222099304199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7420157790184021</v>
+        <v>0.5609714388847351</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5167538523674011</v>
+        <v>0.3042567670345306</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8027262687683105</v>
+        <v>0.6422839760780334</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8521976470947266</v>
+        <v>0.7218508720397949</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>3477910</v>
+        <v>892487</v>
       </c>
       <c r="Z4" t="n">
-        <v>14584543</v>
+        <v>2036603</v>
       </c>
       <c r="AA4" t="n">
-        <v>1106884</v>
+        <v>259401</v>
       </c>
       <c r="AB4" t="n">
-        <v>72388</v>
+        <v>16989</v>
       </c>
       <c r="AC4" t="n">
-        <v>107852</v>
+        <v>37896</v>
       </c>
       <c r="AD4" t="n">
-        <v>12349</v>
+        <v>5048</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>3685882</v>
+        <v>953231</v>
       </c>
       <c r="AG4" t="n">
-        <v>4639979</v>
+        <v>1167484</v>
       </c>
       <c r="AH4" t="n">
-        <v>1846407</v>
+        <v>444916</v>
       </c>
       <c r="AI4" t="n">
-        <v>310818</v>
+        <v>65734</v>
       </c>
       <c r="AJ4" t="n">
-        <v>803283</v>
+        <v>204873</v>
       </c>
       <c r="AK4" t="n">
-        <v>232510</v>
+        <v>62156</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8780803084373474</v>
+        <v>0.8113442063331604</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.7559411525726318</v>
+        <v>0.631259024143219</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.6663616895675659</v>
+        <v>0.517677366733551</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.4132017195224762</v>
+        <v>0.2555539906024933</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.7357413172721863</v>
+        <v>0.5957598090171814</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.7993333339691162</v>
+        <v>0.678075909614563</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>312</v>
+        <v>135</v>
       </c>
       <c r="D5" t="n">
-        <v>92224</v>
+        <v>32166</v>
       </c>
       <c r="E5" t="n">
-        <v>912101</v>
+        <v>254563</v>
       </c>
       <c r="F5" t="n">
-        <v>4149013</v>
+        <v>523565</v>
       </c>
       <c r="G5" t="n">
-        <v>69524</v>
+        <v>16773</v>
       </c>
       <c r="H5" t="n">
-        <v>327671</v>
+        <v>94314</v>
       </c>
       <c r="I5" t="n">
-        <v>28324</v>
+        <v>11418</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2649923</v>
+        <v>799158</v>
       </c>
       <c r="L5" t="n">
-        <v>3549229</v>
+        <v>1075457</v>
       </c>
       <c r="M5" t="n">
-        <v>1430156</v>
+        <v>409369</v>
       </c>
       <c r="N5" t="n">
-        <v>282907</v>
+        <v>64435</v>
       </c>
       <c r="O5" t="n">
-        <v>603939</v>
+        <v>182779</v>
       </c>
       <c r="P5" t="n">
-        <v>171235</v>
+        <v>53790</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999786615371704</v>
+        <v>0.9999507069587708</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9441980123519897</v>
+        <v>0.8981026411056519</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9264287948608398</v>
+        <v>0.8675375580787659</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9700789451599121</v>
+        <v>0.9490051865577698</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9951697587966919</v>
+        <v>0.9930555820465088</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9875084757804871</v>
+        <v>0.9773372411727905</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9964429140090942</v>
+        <v>0.993303120136261</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>135402</v>
+        <v>43217</v>
       </c>
       <c r="Z5" t="n">
-        <v>1169428</v>
+        <v>272950</v>
       </c>
       <c r="AA5" t="n">
-        <v>3710241</v>
+        <v>481192</v>
       </c>
       <c r="AB5" t="n">
-        <v>91461</v>
+        <v>18183</v>
       </c>
       <c r="AC5" t="n">
-        <v>430141</v>
+        <v>102950</v>
       </c>
       <c r="AD5" t="n">
-        <v>42496</v>
+        <v>14442</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>3517701</v>
+        <v>899744</v>
       </c>
       <c r="AG5" t="n">
-        <v>4777383</v>
+        <v>1211821</v>
       </c>
       <c r="AH5" t="n">
-        <v>1868928</v>
+        <v>451742</v>
       </c>
       <c r="AI5" t="n">
-        <v>312475</v>
+        <v>66193</v>
       </c>
       <c r="AJ5" t="n">
-        <v>809435</v>
+        <v>206561</v>
       </c>
       <c r="AK5" t="n">
-        <v>232957</v>
+        <v>62333</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9252914190292358</v>
+        <v>0.8846964240074158</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9023322463035583</v>
+        <v>0.8519448637962341</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9614681601524353</v>
+        <v>0.9442043900489807</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9935358166694641</v>
+        <v>0.9917907118797302</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9832744598388672</v>
+        <v>0.9743980169296265</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9951726198196411</v>
+        <v>0.9922535419464111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>580</v>
+        <v>188</v>
       </c>
       <c r="D6" t="n">
-        <v>52837</v>
+        <v>13509</v>
       </c>
       <c r="E6" t="n">
-        <v>64462</v>
+        <v>17188</v>
       </c>
       <c r="F6" t="n">
-        <v>107371</v>
+        <v>19472</v>
       </c>
       <c r="G6" t="n">
-        <v>249018</v>
+        <v>24402</v>
       </c>
       <c r="H6" t="n">
-        <v>50795</v>
+        <v>11964</v>
       </c>
       <c r="I6" t="n">
-        <v>6862</v>
+        <v>2114</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>67653</v>
+        <v>14535</v>
       </c>
       <c r="Z6" t="n">
-        <v>75733</v>
+        <v>18407</v>
       </c>
       <c r="AA6" t="n">
-        <v>97813</v>
+        <v>18577</v>
       </c>
       <c r="AB6" t="n">
-        <v>219450</v>
+        <v>22644</v>
       </c>
       <c r="AC6" t="n">
-        <v>62527</v>
+        <v>12340</v>
       </c>
       <c r="AD6" t="n">
-        <v>8749</v>
+        <v>2334</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D7" t="n">
-        <v>1635</v>
+        <v>1264</v>
       </c>
       <c r="E7" t="n">
-        <v>72665</v>
+        <v>32059</v>
       </c>
       <c r="F7" t="n">
-        <v>347587</v>
+        <v>100636</v>
       </c>
       <c r="G7" t="n">
-        <v>53463</v>
+        <v>12293</v>
       </c>
       <c r="H7" t="n">
-        <v>2450537</v>
+        <v>326963</v>
       </c>
       <c r="I7" t="n">
-        <v>128389</v>
+        <v>36467</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>4586</v>
+        <v>2906</v>
       </c>
       <c r="Z7" t="n">
-        <v>114737</v>
+        <v>42232</v>
       </c>
       <c r="AA7" t="n">
-        <v>456308</v>
+        <v>109140</v>
       </c>
       <c r="AB7" t="n">
-        <v>65709</v>
+        <v>12324</v>
       </c>
       <c r="AC7" t="n">
-        <v>2245041</v>
+        <v>303181</v>
       </c>
       <c r="AD7" t="n">
-        <v>168095</v>
+        <v>39959</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>4321</v>
+        <v>2236</v>
       </c>
       <c r="F8" t="n">
-        <v>14303</v>
+        <v>6026</v>
       </c>
       <c r="G8" t="n">
-        <v>4063</v>
+        <v>1492</v>
       </c>
       <c r="H8" t="n">
-        <v>148254</v>
+        <v>43962</v>
       </c>
       <c r="I8" t="n">
-        <v>988790</v>
+        <v>139650</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="Z8" t="n">
-        <v>7822</v>
+        <v>3594</v>
       </c>
       <c r="AA8" t="n">
-        <v>22547</v>
+        <v>8241</v>
       </c>
       <c r="AB8" t="n">
-        <v>6007</v>
+        <v>1871</v>
       </c>
       <c r="AC8" t="n">
-        <v>196250</v>
+        <v>48541</v>
       </c>
       <c r="AD8" t="n">
-        <v>927068</v>
+        <v>131107</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
